--- a/Excel/WingConfig.xlsx
+++ b/Excel/WingConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="62">
   <si>
     <t>ID</t>
   </si>
@@ -68,97 +68,151 @@
     <t>6,29,15</t>
   </si>
   <si>
-    <t>5,5,25</t>
-  </si>
-  <si>
-    <t>10,10,50</t>
-  </si>
-  <si>
-    <t>15,15,75</t>
-  </si>
-  <si>
-    <t>20,20,100</t>
-  </si>
-  <si>
-    <t>25,25,125</t>
-  </si>
-  <si>
-    <t>30,30,150</t>
-  </si>
-  <si>
-    <t>35,35,175</t>
-  </si>
-  <si>
-    <t>40,40,200</t>
-  </si>
-  <si>
-    <t>45,45,225</t>
-  </si>
-  <si>
-    <t>50,50,250</t>
-  </si>
-  <si>
-    <t>55,55,275</t>
-  </si>
-  <si>
-    <t>60,60,300</t>
-  </si>
-  <si>
-    <t>65,65,325</t>
-  </si>
-  <si>
-    <t>70,70,350</t>
-  </si>
-  <si>
-    <t>75,75,375</t>
-  </si>
-  <si>
-    <t>80,80,400</t>
-  </si>
-  <si>
-    <t>85,85,425</t>
-  </si>
-  <si>
-    <t>90,90,450</t>
-  </si>
-  <si>
-    <t>95,95,475</t>
-  </si>
-  <si>
-    <t>100,100,500</t>
-  </si>
-  <si>
-    <t>5,5,50</t>
-  </si>
-  <si>
-    <t>105,105,550</t>
+    <t>5,5,250</t>
+  </si>
+  <si>
+    <t>10,10,500</t>
+  </si>
+  <si>
+    <t>15,15,750</t>
+  </si>
+  <si>
+    <t>20,20,1000</t>
+  </si>
+  <si>
+    <t>25,25,1250</t>
+  </si>
+  <si>
+    <t>30,30,1500</t>
+  </si>
+  <si>
+    <t>35,35,1750</t>
+  </si>
+  <si>
+    <t>40,40,2000</t>
+  </si>
+  <si>
+    <t>45,45,2250</t>
+  </si>
+  <si>
+    <t>50,50,2500</t>
+  </si>
+  <si>
+    <t>55,55,2750</t>
+  </si>
+  <si>
+    <t>60,60,3000</t>
+  </si>
+  <si>
+    <t>65,65,3250</t>
+  </si>
+  <si>
+    <t>70,70,3500</t>
+  </si>
+  <si>
+    <t>75,75,3750</t>
+  </si>
+  <si>
+    <t>80,80,4000</t>
+  </si>
+  <si>
+    <t>85,85,4250</t>
+  </si>
+  <si>
+    <t>90,90,4500</t>
+  </si>
+  <si>
+    <t>95,95,4750</t>
+  </si>
+  <si>
+    <t>100,100,5000</t>
+  </si>
+  <si>
+    <t>5,5,500</t>
+  </si>
+  <si>
+    <t>105,105,5500</t>
   </si>
   <si>
     <t>6,29,15,2003</t>
   </si>
   <si>
-    <t>155,155,1100,1</t>
-  </si>
-  <si>
-    <t>5,5,60,1</t>
+    <t>155,155,10500,5</t>
+  </si>
+  <si>
+    <t>5,5,600,5</t>
   </si>
   <si>
     <t>6,29,15,2003,2002</t>
   </si>
   <si>
-    <t>205,205,1700,10,1</t>
-  </si>
-  <si>
-    <t>5,5,70,1,1</t>
+    <t>205,205,16500,55,5</t>
+  </si>
+  <si>
+    <t>5,5,700,5,5</t>
   </si>
   <si>
     <t>6,29,15,2003,2002,2001</t>
   </si>
   <si>
-    <t>255,255,2400,21,10,1</t>
-  </si>
-  <si>
-    <t>5,5,80,1,1,1</t>
+    <t>255,255,23500,105,55,5</t>
+  </si>
+  <si>
+    <t>5,5,800,5,5,5</t>
+  </si>
+  <si>
+    <t>6,29,15,2003,2002,2001,2010</t>
+  </si>
+  <si>
+    <t>305,305,31500,155,105,55,5</t>
+  </si>
+  <si>
+    <t>5,5,900,5,5,5,5</t>
+  </si>
+  <si>
+    <t>6,29,15,2003,2002,2001,2010,2011</t>
+  </si>
+  <si>
+    <t>355,355,40500,205,155,105,55,5</t>
+  </si>
+  <si>
+    <t>5,5,1000,5,5,5,5,5</t>
+  </si>
+  <si>
+    <t>6,29,15,2003,2002,2001,2010,2011,32</t>
+  </si>
+  <si>
+    <t>400,400,50500,255,205,155,105,55,1</t>
+  </si>
+  <si>
+    <t>0,0,2000,10,10,10,5,5,1</t>
+  </si>
+  <si>
+    <t>6,29,15,2003,2002,2001,2010,2011,32,31</t>
+  </si>
+  <si>
+    <t>400,400,70500,355,305,255,155,105,11,1</t>
+  </si>
+  <si>
+    <t>0,0,3000,10,10,10,5,5,1,1</t>
+  </si>
+  <si>
+    <t>6,29,15,2003,2002,2001,2010,2011,32,31,2012</t>
+  </si>
+  <si>
+    <t>400,400,100500,455,405,355,205,155,21,11,10</t>
+  </si>
+  <si>
+    <t>0,0,4000,15,20,10,5,5,1,1,10</t>
+  </si>
+  <si>
+    <t>6,29,15,2003,2002,2001,2010,2011,32,31,2012,2004,2005,2006</t>
+  </si>
+  <si>
+    <t>400,400,180500,755,805,555,305,255,41,31,200,10,10,10</t>
+  </si>
+  <si>
+    <t>0,0,5000,30,40,20,10,0,1,1,20,10,10,10</t>
   </si>
 </sst>
 </file>
@@ -1127,9 +1181,9 @@
     <col min="2" max="2" width="9" style="2"/>
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
     <col min="4" max="5" width="12.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="21.625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="22.5" style="2" customWidth="1"/>
-    <col min="8" max="8" width="15.5" style="2" customWidth="1"/>
+    <col min="6" max="6" width="43.9166666666667" style="2" customWidth="1"/>
+    <col min="7" max="7" width="42.25" style="2" customWidth="1"/>
+    <col min="8" max="8" width="29.1666666666667" style="2" customWidth="1"/>
     <col min="9" max="9" width="11.375" style="2" customWidth="1"/>
     <col min="10" max="10" width="13.25" style="2" customWidth="1"/>
     <col min="11" max="11" width="9.625" style="2" customWidth="1"/>
@@ -1870,12 +1924,162 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" customHeight="1"/>
-    <row r="31" s="1" customFormat="1" customHeight="1"/>
-    <row r="32" s="1" customFormat="1" customHeight="1"/>
-    <row r="33" s="1" customFormat="1" customHeight="1"/>
-    <row r="34" s="1" customFormat="1" customHeight="1"/>
-    <row r="35" s="1" customFormat="1" customHeight="1"/>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C30" s="1">
+        <v>25</v>
+      </c>
+      <c r="D30" s="1">
+        <v>61</v>
+      </c>
+      <c r="E30" s="1">
+        <v>70</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I30" s="1">
+        <v>265</v>
+      </c>
+      <c r="J30" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C31" s="1">
+        <v>26</v>
+      </c>
+      <c r="D31" s="1">
+        <v>71</v>
+      </c>
+      <c r="E31" s="1">
+        <v>80</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="I31" s="1">
+        <v>315</v>
+      </c>
+      <c r="J31" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C32" s="1">
+        <v>27</v>
+      </c>
+      <c r="D32" s="1">
+        <v>81</v>
+      </c>
+      <c r="E32" s="1">
+        <v>90</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I32" s="1">
+        <v>365</v>
+      </c>
+      <c r="J32" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C33" s="1">
+        <v>28</v>
+      </c>
+      <c r="D33" s="1">
+        <v>91</v>
+      </c>
+      <c r="E33" s="1">
+        <v>100</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="I33" s="1">
+        <v>415</v>
+      </c>
+      <c r="J33" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C34" s="1">
+        <v>29</v>
+      </c>
+      <c r="D34" s="1">
+        <v>101</v>
+      </c>
+      <c r="E34" s="1">
+        <v>120</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I34" s="1">
+        <v>465</v>
+      </c>
+      <c r="J34" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C35" s="1">
+        <v>30</v>
+      </c>
+      <c r="D35" s="1">
+        <v>121</v>
+      </c>
+      <c r="E35" s="1">
+        <v>150</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="I35" s="1">
+        <v>515</v>
+      </c>
+      <c r="J35" s="1">
+        <v>5</v>
+      </c>
+    </row>
     <row r="36" s="1" customFormat="1" customHeight="1"/>
     <row r="37" s="1" customFormat="1" customHeight="1"/>
     <row r="38" s="1" customFormat="1" customHeight="1"/>
@@ -1936,7 +2140,7 @@
     <row r="93" s="1" customFormat="1" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 E3 F3 G3 H3 I3 J3 D4 E4 F4 G4 H4 I4 J4 D5 E5 F5 G5 H5 I5 J5 C3:C5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:J5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
